--- a/Segmentation/Segmentation.xlsx
+++ b/Segmentation/Segmentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Jihad\Skin-cancer-papers\Segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DABDBCD2-C522-4671-9A34-E084F5DF26B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE75C7B2-CC46-42B5-B024-627343A78253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
   <si>
     <t>Serial</t>
   </si>
@@ -97,6 +97,105 @@
   </si>
   <si>
     <t>https://arxiv.org/abs/2205.07021</t>
+  </si>
+  <si>
+    <t>Attention-Guided Network with Densely Connected Convolution for Skin Lesion Segmentation</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/1424-8220/21/10/3462</t>
+  </si>
+  <si>
+    <t>ASCU-Net: Attention Gate, Spatial and Channel Attention U-Net for Skin Lesion Segmentation</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/2075-4418/11/3/501</t>
+  </si>
+  <si>
+    <t>Skin Lesion Segmentation and Multiclass Classification Using Deep Learning Features and Improved Moth Flame Optimization</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/2075-4418/11/5/811</t>
+  </si>
+  <si>
+    <t>Automatic lesion segmentation using atrous convolutional deep neural networks in dermoscopic skin cancer images</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1186/s12880-022-00829-y?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>TC-Net: Dual coding network of Transformer and CNN for skin lesion segmentation</t>
+  </si>
+  <si>
+    <t>https://journals.plos.org/plosone/article?id=10.1371%2Fjournal.pone.0277578&amp;utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>MHAU-Net: Skin Lesion Segmentation Based on Multi-Scale Hybrid Residual Attention Network</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/1424-8220/22/22/8701?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>Melanoma segmentation using deep learning with test-time augmentations and conditional random fields</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-022-07885-y</t>
+  </si>
+  <si>
+    <t>Machine learning based skin lesion segmentation method with novel borders and hair removal techniques</t>
+  </si>
+  <si>
+    <t>Machine Learning</t>
+  </si>
+  <si>
+    <t>https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0275781</t>
+  </si>
+  <si>
+    <t>Anti-Aliasing Attention U-net Model for Skin Lesion Segmentation</t>
+  </si>
+  <si>
+    <t>Segmentation and classification of skin lesions using hybrid deep learning method in the Internet of Medical Things</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/2075-4418/13/8/1460</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/doi/full/10.1111/srt.13524</t>
+  </si>
+  <si>
+    <t>Skin lesion segmentation using deep learning algorithm with ant colony optimization</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1186/s12911-024-02686-x?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>An explainable hybrid deep learning framework for precise skin lesion segmentation and multi-class classification</t>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/medicine/articles/10.3389/fmed.2025.1681542/full</t>
+  </si>
+  <si>
+    <t>A deep learning-based dual-branch framework for automated skin lesion segmentation and classification via dermoscopic Images</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-025-21783-z?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>A Hybrid Approach to Skin Cancer Segmentation with the YOLOSAMIC Framework</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/2075-4418/15/4/479?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>Segmentation of Skin Lesions Using Deep YOLO-Family Networks: A Comparison of the Performance of Selected Models on a New Dataset</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/2079-9292/15/8/1545?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>SkinFormer: a hybrid vision transformer and ConvNeXtV2 approach for skin cancer detection and segmentation</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-026-48633-w?utm_source=chatgpt.com</t>
   </si>
 </sst>
 </file>
@@ -417,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="E5:I26"/>
+  <dimension ref="E5:I29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" width="8.88671875" style="1"/>
@@ -580,69 +679,276 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="5:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="E14" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F14" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="5:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="E15" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F15" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="5:9" ht="72" x14ac:dyDescent="0.3">
       <c r="E16" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="5:9" ht="72" x14ac:dyDescent="0.3">
       <c r="E17" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F17" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="5:9" ht="72" x14ac:dyDescent="0.3">
       <c r="E18" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="5:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="E19" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="5:9" ht="72" x14ac:dyDescent="0.3">
       <c r="E20" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F20" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="5:9" ht="72" x14ac:dyDescent="0.3">
       <c r="E21" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F21" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="5:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="E22" s="1">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F22" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="5:9" ht="72" x14ac:dyDescent="0.3">
       <c r="E23" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F23" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="5:9" ht="72" x14ac:dyDescent="0.3">
       <c r="E24" s="1">
         <v>19</v>
       </c>
-    </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="5:9" ht="72" x14ac:dyDescent="0.3">
       <c r="E25" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F25" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="5:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="E26" s="1">
         <v>21</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="5:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E27" s="1">
+        <v>22</v>
+      </c>
+      <c r="F27" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="5:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="E28" s="1">
+        <v>23</v>
+      </c>
+      <c r="F28" s="1">
+        <v>2026</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="5:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="E29" s="1">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
